--- a/launch/2026-10/import/otto-nl-part1.xlsx
+++ b/launch/2026-10/import/otto-nl-part1.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU18"/>
+  <dimension ref="A1:AU22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
@@ -452,10 +452,10 @@
     <col width="26" customWidth="1" min="30" max="30"/>
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
     <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="32" customWidth="1" min="36" max="36"/>
+    <col width="31" customWidth="1" min="36" max="36"/>
     <col width="26" customWidth="1" min="37" max="37"/>
     <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NL · a1 · Reels without the filming</t>
+          <t>NL · a1 · Automate your marketing</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Reels, without the filming</t>
+          <t>Automate your marketing</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>You know reels work. You just don't have an evening to film and edit them. Otto makes them from your own website.</t>
+          <t>Automate your marketing: posts, reels and stories every week, ads every day, one report at 07:35. You approve with one tap.</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Posts, reels, stories and ads</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NL · a1 · Reels without the filming</t>
+          <t>NL · a1 · Automate your marketing</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Your website, as a reel</t>
+          <t>Take your marketing to the next level</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Your menu, your products, your opening hours: it's all on your website. Otto turns it into reels. No filming needed.</t>
+          <t>From posting when you remember to a plan that runs every day. Otto plans, writes, designs and posts. You run the business.</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Posts, reels, stories and ads</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NL · a1 · Reels without the filming</t>
+          <t>NL · a1 · Automate your marketing</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Reels, without the filming</t>
+          <t>Automate your marketing</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Try Otto free for 7 days: your first reels, made from your own site. Nothing goes live without your approval.</t>
+          <t>Your marketing department in one app: posts, reels, stories and ads. 7 days free, then €79 a month. Cancel anytime.</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Posts, reels, stories and ads</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NL · a1 · Reels without the filming</t>
+          <t>NL · a1 · Automate your marketing</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Your website, as a reel</t>
+          <t>Take your marketing to the next level</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>You know reels work. You just don't have an evening to film and edit them. Otto makes them from your own website.</t>
+          <t>Automate your marketing: posts, reels and stories every week, ads every day, one report at 07:35. You approve with one tap.</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Posts, reels, stories and ads</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NL · a1 · Reels without the filming</t>
+          <t>NL · a1 · Automate your marketing</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>nl-a1-search</t>
+          <t>nl-a1-before</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Reels, without the filming</t>
+          <t>Automate your marketing</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Your menu, your products, your opening hours: it's all on your website. Otto turns it into reels. No filming needed.</t>
+          <t>From posting when you remember to a plan that runs every day. Otto plans, writes, designs and posts. You run the business.</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Posts, reels, stories and ads</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>nl-a1-search-4x5.jpg</t>
+          <t>nl-a1-before-4x5.jpg</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a1-search</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a1-before</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr"/>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NL · a1 · Reels without the filming</t>
+          <t>NL · a1 · Automate your marketing</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>nl-a1-number</t>
+          <t>nl-a1-search</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Your website, as a reel</t>
+          <t>Take your marketing to the next level</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Try Otto free for 7 days: your first reels, made from your own site. Nothing goes live without your approval.</t>
+          <t>Your marketing department in one app: posts, reels, stories and ads. 7 days free, then €79 a month. Cancel anytime.</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Posts, reels, stories and ads</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>nl-a1-number-4x5.jpg</t>
+          <t>nl-a1-search-4x5.jpg</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a1-number</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a1-search</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NL · a2 · The 07:35 message</t>
+          <t>NL · a1 · Automate your marketing</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>nl-a2-texts-v</t>
+          <t>nl-a1-premium</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>One message at 07:35</t>
+          <t>Automate your marketing</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Every morning at 07:35, Otto tells you what your ads cost yesterday, what they brought in and which posts are waiting.</t>
+          <t>Automate your marketing: posts, reels and stories every week, ads every day, one report at 07:35. You approve with one tap.</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>Your marketing, in one message</t>
+          <t>Posts, reels, stories and ads</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2076,22 +2076,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>automate-1x1.jpg</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Video Page Post Ad</t>
+          <t>Link Page Post Ad</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-texts-v</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>nl-a2-texts-v-9x16.mp4</t>
-        </is>
-      </c>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a1-premium</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NL · a2 · The 07:35 message</t>
+          <t>NL · a2 · Stop paying agency prices</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>nl-a2-big-v</t>
+          <t>nl-a2-versus-v</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Know by 07:35 every morning</t>
+          <t>Stop paying agency prices</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>A monthly PDF tells you too late. Otto sends one short message every morning at 07:35. Read it with your coffee.</t>
+          <t>€500–1,500 a month, just for posts. That's what a social media agency charges. Otto does posts and ads for €79 a month.</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>Your marketing, in one message</t>
+          <t>€79 a month, excl. VAT</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-big-v</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-versus-v</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>nl-a2-big-v-9x16.mp4</t>
+          <t>nl-a2-versus-v-9x16.mp4</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NL · a2 · The 07:35 message</t>
+          <t>NL · a2 · Stop paying agency prices</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>nl-a2-notes-v</t>
+          <t>nl-a2-search-v</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>One message at 07:35</t>
+          <t>Your marketing team for €79 a month</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Your 07:35 report comes in English, Dutch or German: your choice. If something drops, you know the next morning.</t>
+          <t>Paying an agency to post for you? Otto plans, writes, designs and posts, and runs your ads too. All for €79 a month.</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>Your marketing, in one message</t>
+          <t>€79 a month, excl. VAT</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-notes-v</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-search-v</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>nl-a2-notes-v-9x16.mp4</t>
+          <t>nl-a2-search-v-9x16.mp4</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>NL · a2 · The 07:35 message</t>
+          <t>NL · a2 · Stop paying agency prices</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>nl-a2-compare</t>
+          <t>nl-a2-big-v</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Know by 07:35 every morning</t>
+          <t>Stop paying agency prices</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Every morning at 07:35, Otto tells you what your ads cost yesterday, what they brought in and which posts are waiting.</t>
+          <t>Posts, reels, stories and ads, without the agency invoice. €79 a month, no contract, cancel anytime.</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>Your marketing, in one message</t>
+          <t>€79 a month, excl. VAT</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2679,22 +2679,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>nl-a2-compare-4x5.jpg</t>
-        </is>
-      </c>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Link Page Post Ad</t>
+          <t>Video Page Post Ad</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-compare</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-big-v</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>nl-a2-big-v-9x16.mp4</t>
+        </is>
+      </c>
       <c r="AR11" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>NL · a2 · The 07:35 message</t>
+          <t>NL · a2 · Stop paying agency prices</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>nl-a2-macro</t>
+          <t>nl-a2-compare</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>One message at 07:35</t>
+          <t>Your marketing team for €79 a month</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>A monthly PDF tells you too late. Otto sends one short message every morning at 07:35. Read it with your coffee.</t>
+          <t>€500–1,500 a month, just for posts. That's what a social media agency charges. Otto does posts and ads for €79 a month.</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>Your marketing, in one message</t>
+          <t>€79 a month, excl. VAT</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>nl-a2-macro-4x5.jpg</t>
+          <t>nl-a2-compare-4x5.jpg</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-macro</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-compare</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>NL · a2 · The 07:35 message</t>
+          <t>NL · a2 · Stop paying agency prices</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>nl-a2-notes</t>
+          <t>nl-a2-product</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Know by 07:35 every morning</t>
+          <t>Stop paying agency prices</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Your 07:35 report comes in English, Dutch or German: your choice. If something drops, you know the next morning.</t>
+          <t>Paying an agency to post for you? Otto plans, writes, designs and posts, and runs your ads too. All for €79 a month.</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Your marketing, in one message</t>
+          <t>€79 a month, excl. VAT</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>nl-a2-notes-4x5.jpg</t>
+          <t>nl-a2-product-4x5.jpg</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-notes</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-product</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr"/>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NL · a3 · Local, not translated</t>
+          <t>NL · a2 · Stop paying agency prices</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>nl-a3-notes-v</t>
+          <t>nl-a2-number</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Dutch posts. Not translated.</t>
+          <t>Your marketing team for €79 a month</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Your customers read Dutch, so your posts should sound Dutch, not like translated English. Otto writes them for your town.</t>
+          <t>Posts, reels, stories and ads, without the agency invoice. €79 a month, no contract, cancel anytime.</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>For shops, cafés and salons</t>
+          <t>€79 a month, excl. VAT</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3282,22 +3282,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>nl-a2-number-4x5.jpg</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Video Page Post Ad</t>
+          <t>Link Page Post Ad</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-notes-v</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>nl-a3-notes-v-9x16.mp4</t>
-        </is>
-      </c>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-number</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>NL · a3 · Local, not translated</t>
+          <t>NL · a2 · Stop paying agency prices</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>nl-a3-versus-v</t>
+          <t>nl-a2-premium</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Sounds like your business</t>
+          <t>Stop paying agency prices</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>‘We are super excited to share…’ Sound familiar? That's translated marketing. Otto writes the way you talk.</t>
+          <t>€500–1,500 a month, just for posts. That's what a social media agency charges. Otto does posts and ads for €79 a month.</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>For shops, cafés and salons</t>
+          <t>€79 a month, excl. VAT</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3483,22 +3483,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>agency-1x1.jpg</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Video Page Post Ad</t>
+          <t>Link Page Post Ad</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-versus-v</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>nl-a3-versus-v-9x16.mp4</t>
-        </is>
-      </c>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a2-premium</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NL · a3 · Local, not translated</t>
+          <t>NL · a3 · Your ads, reported at 07:35</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>nl-a3-big-v</t>
+          <t>nl-a3-texts-v</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Dutch posts. Not translated.</t>
+          <t>Your ads report, every day at 07:35</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Otto reads your website, your prices and your reviews, then writes posts that sound like you, in Dutch or English.</t>
+          <t>Every morning at 07:35: what your ads cost yesterday and what they brought in. Spend, clicks, enquiries. One message.</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>For shops, cafés and salons</t>
+          <t>One report, every morning</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-big-v</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-texts-v</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>nl-a3-big-v-9x16.mp4</t>
+          <t>nl-a3-texts-v-9x16.mp4</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>NL · a3 · Local, not translated</t>
+          <t>NL · a3 · Your ads, reported at 07:35</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>nl-a3-product</t>
+          <t>nl-a3-big-v</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Sounds like your business</t>
+          <t>Know what your ads did by 07:35</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Your customers read Dutch, so your posts should sound Dutch, not like translated English. Otto writes them for your town.</t>
+          <t>One campaign, ads for every angle, and one message at 07:35 that says which one works. Approve, pause, done.</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>For shops, cafés and salons</t>
+          <t>One report, every morning</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3885,22 +3885,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>nl-a3-product-4x5.jpg</t>
-        </is>
-      </c>
+      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Link Page Post Ad</t>
+          <t>Video Page Post Ad</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-product</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr"/>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-big-v</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>nl-a3-big-v-9x16.mp4</t>
+        </is>
+      </c>
       <c r="AR17" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>NL · a3 · Local, not translated</t>
+          <t>NL · a3 · Your ads, reported at 07:35</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>nl-a3-post</t>
+          <t>nl-a3-notes-v</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Dutch posts. Not translated.</t>
+          <t>Your ads report, every day at 07:35</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>‘We are super excited to share…’ Sound familiar? That's translated marketing. Otto writes the way you talk.</t>
+          <t>Your 07:35 report comes by e-mail, in Telegram or in the app. In English, Dutch or German: your choice.</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>For shops, cafés and salons</t>
+          <t>One report, every morning</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4086,38 +4086,842 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>nl-a3-post-4x5.jpg</t>
-        </is>
-      </c>
+      <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
         <is>
+          <t>Video Page Post Ad</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-notes-v</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>nl-a3-notes-v-9x16.mp4</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>x:{INSTAGRAM_ID}</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>LEARN_MORE</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OTTO · NL · Launch · 2026-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PAUSED</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Outcome Leads</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AUCTION</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Lowest Cost</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NL · a3 · Your ads, reported at 07:35</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>WEBSITE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>o:{PAGE_ID}</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>COMPLETE_REGISTRATION</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>https://{DOMAIN}/</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>65</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>mobile, desktop</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>OFFSITE_CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>[{"event_type":"CLICK_THROUGH","window_days":7},{"event_type":"VIEW_THROUGH","window_days":1}]</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>nl-a3-macro</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Know what your ads did by 07:35</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Every morning at 07:35: what your ads cost yesterday and what they brought in. Spend, clicks, enquiries. One message.</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>{DOMAIN}</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>One report, every morning</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>nl-a3-macro-4x5.jpg</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
           <t>Link Page Post Ad</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-post</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr">
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-macro</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
+      <c r="AS19" t="inlineStr">
         <is>
           <t>LEARN_MORE</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
+      <c r="AT19" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AU18" t="inlineStr">
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OTTO · NL · Launch · 2026-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PAUSED</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Outcome Leads</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>AUCTION</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Lowest Cost</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NL · a3 · Your ads, reported at 07:35</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>WEBSITE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>o:{PAGE_ID}</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>COMPLETE_REGISTRATION</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>https://{DOMAIN}/</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>65</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>mobile, desktop</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>OFFSITE_CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>[{"event_type":"CLICK_THROUGH","window_days":7},{"event_type":"VIEW_THROUGH","window_days":1}]</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>nl-a3-compare</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Your ads report, every day at 07:35</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>One campaign, ads for every angle, and one message at 07:35 that says which one works. Approve, pause, done.</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>{DOMAIN}</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>One report, every morning</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>nl-a3-compare-4x5.jpg</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Link Page Post Ad</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-compare</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>x:{INSTAGRAM_ID}</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>LEARN_MORE</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OTTO · NL · Launch · 2026-10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PAUSED</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Outcome Leads</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AUCTION</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Lowest Cost</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NL · a3 · Your ads, reported at 07:35</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>WEBSITE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>o:{PAGE_ID}</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>COMPLETE_REGISTRATION</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>https://{DOMAIN}/</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>65</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>mobile, desktop</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>OFFSITE_CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>[{"event_type":"CLICK_THROUGH","window_days":7},{"event_type":"VIEW_THROUGH","window_days":1}]</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>nl-a3-notes</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Know what your ads did by 07:35</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Your 07:35 report comes by e-mail, in Telegram or in the app. In English, Dutch or German: your choice.</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>{DOMAIN}</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>One report, every morning</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>nl-a3-notes-4x5.jpg</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Link Page Post Ad</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-notes</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>x:{INSTAGRAM_ID}</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>LEARN_MORE</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OTTO · NL · Launch · 2026-10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PAUSED</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Outcome Leads</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>AUCTION</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Lowest Cost</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NL · a3 · Your ads, reported at 07:35</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>WEBSITE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>o:{PAGE_ID}</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>COMPLETE_REGISTRATION</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>https://{DOMAIN}/</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>25</v>
+      </c>
+      <c r="W22" t="n">
+        <v>65</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>mobile, desktop</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>OFFSITE_CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>[{"event_type":"CLICK_THROUGH","window_days":7},{"event_type":"VIEW_THROUGH","window_days":1}]</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>nl-a3-premium</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Your ads report, every day at 07:35</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Every morning at 07:35: what your ads cost yesterday and what they brought in. Spend, clicks, enquiries. One message.</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>{DOMAIN}</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>One report, every morning</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>report-1x1.jpg</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Link Page Post Ad</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_nl_launch&amp;utm_content=nl-a3-premium</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>x:{INSTAGRAM_ID}</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>LEARN_MORE</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
